--- a/DOC/Traducciones.xlsx
+++ b/DOC/Traducciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJS\EDExplorer\DOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD5994-3C38-4EF7-865E-B7A9C8EF4751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD6350-4BFC-403C-9C17-1097CF9E8DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="6" xr2:uid="{1A1EC2D9-168A-4070-97B0-8737BCB54E6F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{1A1EC2D9-168A-4070-97B0-8737BCB54E6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Try" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="EDExplorerFRM" sheetId="5" r:id="rId4"/>
     <sheet name="Pantalla Lista Alertas" sheetId="6" r:id="rId5"/>
     <sheet name="Pantalla de Configuración" sheetId="7" r:id="rId6"/>
-    <sheet name="Pantalla About" sheetId="8" r:id="rId7"/>
+    <sheet name="CFG" sheetId="9" r:id="rId7"/>
+    <sheet name="Pantalla About" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1175">
   <si>
     <t>Key</t>
   </si>
@@ -3427,6 +3428,174 @@
 O relato de incidentes ou solicitação de melhorias pode ser feito em =&gt; https://github.com/3navis/EDExplorer-Follow-up_x000D_
 _x000D_
 Modelagem gráfica que resolve um desafio do computador que apareceu na seção 'jogos de computador' da revista Investigación y Ciencia (1986). </t>
+  </si>
+  <si>
+    <t>str_ATENCION_Cambio_de_Idioma</t>
+  </si>
+  <si>
+    <t>ATENCION - Cambio de Idioma</t>
+  </si>
+  <si>
+    <t>str_Probando_el_volumen_del_Locutor</t>
+  </si>
+  <si>
+    <t>Probando el volumen del Locutor.</t>
+  </si>
+  <si>
+    <t>str_Prueba_de_Notificaciones</t>
+  </si>
+  <si>
+    <t>Prueba de Notificaciones</t>
+  </si>
+  <si>
+    <t>str_Prueba_de_Notificaciones_dos_neas</t>
+  </si>
+  <si>
+    <t>Prueba de Notificaciones
+dos líneas.</t>
+  </si>
+  <si>
+    <t>str_This_is_the_notification_text</t>
+  </si>
+  <si>
+    <t>This is the notification text</t>
+  </si>
+  <si>
+    <t>str_This_is_the_notification_title</t>
+  </si>
+  <si>
+    <t>This is the notification title</t>
+  </si>
+  <si>
+    <t>ADI - Hizkuntza aldaketa</t>
+  </si>
+  <si>
+    <t>Esatariaren bolumena probatzen.</t>
+  </si>
+  <si>
+    <t>Jakinarazpen Proba</t>
+  </si>
+  <si>
+    <t>Jakinarazpenen egiaztagiria_x000D_
+bi lerro .</t>
+  </si>
+  <si>
+    <t>Hau da jakinarazpen testua</t>
+  </si>
+  <si>
+    <t>Hau da jakinarazpenaren izenburua</t>
+  </si>
+  <si>
+    <t>ATENCIÓ - Canvi d'idioma</t>
+  </si>
+  <si>
+    <t>Provant el volum de l'Locutor.</t>
+  </si>
+  <si>
+    <t>Prova de Notificacions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prova de Notificacions_x000D_
+dues línies. </t>
+  </si>
+  <si>
+    <t>ATENÇÃO - Mudança de idioma</t>
+  </si>
+  <si>
+    <t>Testando o volume do Anunciador.</t>
+  </si>
+  <si>
+    <t>Teste de Notificação</t>
+  </si>
+  <si>
+    <t>Prova de Notificações_x000D_
+duas linhas.</t>
+  </si>
+  <si>
+    <t>Este é o texto de notificação</t>
+  </si>
+  <si>
+    <t>Este é o título da notificação</t>
+  </si>
+  <si>
+    <t>ATTENTION - Language change</t>
+  </si>
+  <si>
+    <t>Testing the Announcer's volume.</t>
+  </si>
+  <si>
+    <t>Notification Test</t>
+  </si>
+  <si>
+    <t>Proof of Notifications_x000D_
+two lines.</t>
+  </si>
+  <si>
+    <t>ATTENTION - Changement de langue</t>
+  </si>
+  <si>
+    <t>Tester le volume de l'annonceur.</t>
+  </si>
+  <si>
+    <t>Test de notification</t>
+  </si>
+  <si>
+    <t>Preuve de notification_x000D_
+deux lignes.</t>
+  </si>
+  <si>
+    <t>Ceci est le texte de notification</t>
+  </si>
+  <si>
+    <t>Ceci est le titre de la notification</t>
+  </si>
+  <si>
+    <t>Comment.ja-JP</t>
+  </si>
+  <si>
+    <t>.ja-JP</t>
+  </si>
+  <si>
+    <t>str_confirmar_cambio_idioma</t>
+  </si>
+  <si>
+    <t>Esta acción resetea todos los textos de las Alertas y reinicia la App. ¿Quiere continuar?</t>
+  </si>
+  <si>
+    <t>Aquesta acció reseteja tots els textos de les Alertes i reinicia l'App. Voleu continuar?</t>
+  </si>
+  <si>
+    <t>This action resets all text alerts and restarts the App. Do you want to continue?</t>
+  </si>
+  <si>
+    <t>Ekintza honek Alerten testu guztiak berrezartzen ditu eta aplikazioa berrabiarazten du. Jarraitu nahi duzu?</t>
+  </si>
+  <si>
+    <t>Cette action réinitialise toutes les alertes texte et redémarre l'application. Voulez-vous continuer ?</t>
+  </si>
+  <si>
+    <t>Esta acção reinicia todos os alertas de texto e reinicia a aplicação. Quer continuar?</t>
+  </si>
+  <si>
+    <t>注意-言語の変更</t>
+  </si>
+  <si>
+    <t>アナウンサーの音量をテストします。</t>
+  </si>
+  <si>
+    <t>通知テスト</t>
+  </si>
+  <si>
+    <t>これは通知テキストです</t>
+  </si>
+  <si>
+    <t>これは通知のタイトルです</t>
+  </si>
+  <si>
+    <t>このアクションにより、すべてのアラートテキストがリセットされ、アプリが再起動します。続行しますか？</t>
+  </si>
+  <si>
+    <t>「通知テスト2行。」</t>
   </si>
 </sst>
 </file>
@@ -10544,6 +10713,246 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEA8753-44E8-4462-954C-702E9B580C63}">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O3" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1166</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F91C229A-81DB-43BD-877D-C51DF88FE12D}">
   <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10632,7 +11041,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1104</v>
       </c>
